--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4901,140 +4901,148 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>114.98375795921503</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>285.01624204078496</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>36637.604193435269</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>3362.3958065647312</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>43600</v>
+        <v>41200</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>114.09616552393449</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>285.90383447606553</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>36351.700358959206</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>3648.2996410407941</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>36922.620435476056</v>
+        <v>35199.153684934674</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>113.20580896431662</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>286.79419103568341</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>36064.906167923524</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>3935.0938320764762</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3077.3795645239443</v>
+        <v>4800.8463150653261</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>112.31267967237527</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>287.68732032762472</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>35777.218847595897</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>4222.7811524041026</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -5045,31 +5053,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46202</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>111.41676901331751</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>288.58323098668251</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>35488.635616609216</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>4511.3643833907845</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -5080,31 +5090,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>110.51806832546009</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>289.48193167453991</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>35199.153684934674</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>4800.8463150653261</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4901,7 +4901,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>41200</v>
+        <v>38800</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>35199.153684934674</v>
+        <v>33443.232040642419</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4800.8463150653261</v>
+        <v>6556.7679593575813</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -5120,173 +5120,185 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46208</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
+        <v>109.61656892014567</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>290.38343107985435</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>34908.770253854818</v>
+      </c>
+      <c r="H19" s="21">
+        <f t="shared" si="2"/>
+        <v>5091.2297461451817</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>108.71226208165889</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>291.28773791834112</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>34617.482515936477</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
+        <v>5382.5174840635227</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46208</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D21" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="1"/>
+        <v>107.80513906714206</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>292.19486093285792</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>34325.287655003616</v>
+      </c>
+      <c r="H21" s="21">
+        <f t="shared" si="2"/>
+        <v>5674.7123449963838</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D22" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="1"/>
+        <v>106.89519110651061</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>293.10480889348941</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>34032.182846110125</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="2"/>
+        <v>5967.817153889875</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46208</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D23" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E23" s="21">
+        <f t="shared" si="1"/>
+        <v>105.98240940236836</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>294.01759059763162</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>33738.165255512497</v>
+      </c>
+      <c r="H23" s="21">
+        <f t="shared" si="2"/>
+        <v>6261.8347444875035</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46208</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D24" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="1"/>
+        <v>105.06678512992245</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>294.93321487007756</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>33443.232040642419</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="2"/>
+        <v>6556.7679593575813</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4901,7 +4901,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>38800</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>33443.232040642419</v>
+        <v>31654.244339008208</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6556.7679593575813</v>
+        <v>8345.755660991792</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -5302,171 +5302,183 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46214</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D25" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" si="1"/>
+        <v>104.14830943689796</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>295.85169056310201</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>33147.380350079315</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="2"/>
+        <v>6852.6196499206853</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A26" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B26" s="23">
+        <f t="shared" si="3"/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D26" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="1"/>
+        <v>103.22697344345241</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="5"/>
+        <v>296.77302655654762</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="4"/>
+        <v>32850.607323522767</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="2"/>
+        <v>7149.3926764772332</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A27" s="19">
+        <v>46214</v>
+      </c>
+      <c r="B27" s="24">
+        <f t="shared" si="3"/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D27" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E27" s="21">
+        <f t="shared" si="1"/>
+        <v>102.30276824208987</v>
+      </c>
+      <c r="F27" s="21">
+        <f t="shared" si="5"/>
+        <v>297.69723175791012</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="4"/>
+        <v>32552.910091764857</v>
+      </c>
+      <c r="H27" s="21">
+        <f t="shared" si="2"/>
+        <v>7447.0899082351425</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D28" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="1"/>
+        <v>101.37568489757484</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>298.62431510242516</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>32254.285776662433</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="2"/>
+        <v>7745.7142233375671</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46214</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D29" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E29" s="21">
+        <f t="shared" si="1"/>
+        <v>100.4457144468459</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>299.5542855531541</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>31954.73149110928</v>
+      </c>
+      <c r="H29" s="21">
+        <f t="shared" si="2"/>
+        <v>8045.2685088907201</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46214</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D30" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="1"/>
+        <v>99.512847898928982</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>300.48715210107105</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>31654.244339008208</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" si="2"/>
+        <v>8345.755660991792</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4901,7 +4901,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>36400</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>31654.244339008208</v>
+        <v>29831.567907516048</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>8345.755660991792</v>
+        <v>10168.432092483952</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -5482,171 +5482,183 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46222</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D31" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E31" s="21">
+        <f t="shared" si="1"/>
+        <v>98.577076234850495</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>301.42292376514951</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>31352.821415243059</v>
+      </c>
+      <c r="H31" s="21">
+        <f t="shared" si="2"/>
+        <v>8647.1785847569408</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46222</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D32" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="1"/>
+        <v>97.638390407550176</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>302.36160959244984</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>31050.459805650611</v>
+      </c>
+      <c r="H32" s="4">
+        <f t="shared" si="2"/>
+        <v>8949.5401943493889</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46222</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D33" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="1"/>
+        <v>96.696781341793496</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>303.3032186582065</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>30747.156586992405</v>
+      </c>
+      <c r="H33" s="21">
+        <f t="shared" si="2"/>
+        <v>9252.8434130075948</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46222</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D34" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="1"/>
+        <v>95.752239934084059</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>304.24776006591594</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>30442.90882692649</v>
+      </c>
+      <c r="H34" s="4">
+        <f t="shared" si="2"/>
+        <v>9557.0911730735097</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46222</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D35" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E35" s="21">
+        <f t="shared" si="1"/>
+        <v>94.804757052575482</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>305.1952429474245</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>30137.713583979064</v>
+      </c>
+      <c r="H35" s="21">
+        <f t="shared" si="2"/>
+        <v>9862.2864160209356</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A36" s="2">
+        <v>46222</v>
+      </c>
+      <c r="B36" s="23">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E36" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D36" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="1"/>
+        <v>93.854323536983145</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>306.14567646301685</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="4"/>
+        <v>29831.567907516048</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" si="2"/>
+        <v>10168.432092483952</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="4" r:id="rId1"/>
     <sheet name="188" sheetId="6" r:id="rId2"/>
+    <sheet name="204" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
   <si>
     <t>Date</t>
   </si>
@@ -92,6 +93,21 @@
   </si>
   <si>
     <t>Principal Outstanding</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Weekly Rate</t>
+  </si>
+  <si>
+    <t>Weeks</t>
+  </si>
+  <si>
+    <t>LatestWeek</t>
+  </si>
+  <si>
+    <t>kamala</t>
   </si>
 </sst>
 </file>
@@ -4901,7 +4917,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4938,7 +4954,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>34000</v>
+        <v>26800</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>29831.567907516048</v>
+        <v>24155.002294956197</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5012,7 +5028,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>10168.432092483952</v>
+        <v>15844.997705043803</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -5662,507 +5678,543 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="B37" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A37" s="19">
+        <v>46228</v>
+      </c>
+      <c r="B37" s="24">
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="C37" s="20"/>
-      <c r="D37" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E37" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F37" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H37" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D37" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E37" s="21">
+        <f t="shared" si="1"/>
+        <v>92.900930198495701</v>
+      </c>
+      <c r="F37" s="21">
+        <f t="shared" si="5"/>
+        <v>307.0990698015043</v>
+      </c>
+      <c r="G37" s="21">
+        <f t="shared" si="4"/>
+        <v>29524.468837714543</v>
+      </c>
+      <c r="H37" s="21">
+        <f t="shared" si="2"/>
+        <v>10475.531162285457</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A38" s="2">
+        <v>46228</v>
+      </c>
+      <c r="B38" s="23">
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E38" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F38" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G38" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H38" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D38" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="1"/>
+        <v>91.944567819686085</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="5"/>
+        <v>308.05543218031391</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="4"/>
+        <v>29216.413405534229</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="2"/>
+        <v>10783.586594465771</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A39" s="19">
+        <v>46228</v>
+      </c>
+      <c r="B39" s="24">
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E39" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D39" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E39" s="21">
+        <f t="shared" si="1"/>
+        <v>90.985227154422546</v>
+      </c>
+      <c r="F39" s="21">
+        <f t="shared" si="5"/>
+        <v>309.01477284557745</v>
+      </c>
+      <c r="G39" s="21">
+        <f t="shared" si="4"/>
+        <v>28907.398632688652</v>
+      </c>
+      <c r="H39" s="21">
+        <f t="shared" si="2"/>
+        <v>11092.601367311348</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46228</v>
+      </c>
+      <c r="B40" s="23">
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E40" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D40" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="1"/>
+        <v>90.022898927779181</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="5"/>
+        <v>309.97710107222082</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>28597.42153161643</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="2"/>
+        <v>11402.57846838357</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A41" s="19">
+        <v>46228</v>
+      </c>
+      <c r="B41" s="24">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="C41" s="20"/>
-      <c r="D41" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E41" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F41" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D41" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E41" s="21">
+        <f t="shared" si="1"/>
+        <v>89.057573835946272</v>
+      </c>
+      <c r="F41" s="21">
+        <f t="shared" si="5"/>
+        <v>310.9424261640537</v>
+      </c>
+      <c r="G41" s="21">
+        <f t="shared" si="4"/>
+        <v>28286.479105452378</v>
+      </c>
+      <c r="H41" s="21">
+        <f t="shared" si="2"/>
+        <v>11713.520894547622</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A42" s="2">
+        <v>46228</v>
+      </c>
+      <c r="B42" s="23">
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D42" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="1"/>
+        <v>88.089242546140369</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="5"/>
+        <v>311.91075745385962</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>27974.568347998516</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="2"/>
+        <v>12025.431652001484</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A43" s="19">
+        <v>46234</v>
+      </c>
+      <c r="B43" s="24">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="C43" s="20"/>
-      <c r="D43" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E43" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F43" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D43" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E43" s="21">
+        <f t="shared" si="1"/>
+        <v>87.117895696513983</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="5"/>
+        <v>312.88210430348602</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>27661.686243695029</v>
+      </c>
+      <c r="H43" s="21">
+        <f t="shared" si="2"/>
+        <v>12338.313756304971</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A44" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B44" s="23">
+        <f t="shared" si="3"/>
+        <v>43</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E44" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F44" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G44" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H44" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D44" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" si="1"/>
+        <v>86.143523896065204</v>
+      </c>
+      <c r="F44" s="4">
+        <f t="shared" si="5"/>
+        <v>313.85647610393482</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="4"/>
+        <v>27347.829767591094</v>
+      </c>
+      <c r="H44" s="4">
+        <f t="shared" si="2"/>
+        <v>12652.170232408906</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A45" s="19">
+        <v>46234</v>
+      </c>
+      <c r="B45" s="24">
+        <f t="shared" si="3"/>
+        <v>44</v>
       </c>
       <c r="C45" s="20"/>
-      <c r="D45" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E45" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F45" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G45" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H45" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D45" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E45" s="21">
+        <f t="shared" si="1"/>
+        <v>85.166117724546766</v>
+      </c>
+      <c r="F45" s="21">
+        <f t="shared" si="5"/>
+        <v>314.83388227545322</v>
+      </c>
+      <c r="G45" s="21">
+        <f t="shared" si="4"/>
+        <v>27032.995885315642</v>
+      </c>
+      <c r="H45" s="21">
+        <f t="shared" si="2"/>
+        <v>12967.004114684358</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A46" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B46" s="23">
+        <f t="shared" si="3"/>
+        <v>45</v>
       </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E46" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F46" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G46" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H46" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D46" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="1"/>
+        <v>84.18566773237508</v>
+      </c>
+      <c r="F46" s="4">
+        <f t="shared" si="5"/>
+        <v>315.81433226762493</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="4"/>
+        <v>26717.181553048016</v>
+      </c>
+      <c r="H46" s="4">
+        <f t="shared" si="2"/>
+        <v>13282.818446951984</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A47" s="19">
+        <v>46234</v>
+      </c>
+      <c r="B47" s="24">
+        <f t="shared" si="3"/>
+        <v>46</v>
       </c>
       <c r="C47" s="20"/>
-      <c r="D47" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E47" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F47" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G47" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H47" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D47" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E47" s="21">
+        <f t="shared" si="1"/>
+        <v>83.202164440538809</v>
+      </c>
+      <c r="F47" s="21">
+        <f t="shared" si="5"/>
+        <v>316.79783555946119</v>
+      </c>
+      <c r="G47" s="21">
+        <f t="shared" si="4"/>
+        <v>26400.383717488556</v>
+      </c>
+      <c r="H47" s="21">
+        <f t="shared" si="2"/>
+        <v>13599.616282511444</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A48" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B48" s="23">
+        <f t="shared" si="3"/>
+        <v>47</v>
       </c>
       <c r="C48" s="3"/>
-      <c r="D48" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E48" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F48" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G48" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H48" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D48" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="1"/>
+        <v>82.215598340507285</v>
+      </c>
+      <c r="F48" s="4">
+        <f t="shared" si="5"/>
+        <v>317.78440165949269</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="4"/>
+        <v>26082.599315829062</v>
+      </c>
+      <c r="H48" s="4">
+        <f t="shared" si="2"/>
+        <v>13917.400684170938</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A49" s="19">
+        <v>46240</v>
+      </c>
+      <c r="B49" s="24">
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="C49" s="20"/>
-      <c r="D49" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E49" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F49" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G49" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H49" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D49" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E49" s="21">
+        <f t="shared" si="1"/>
+        <v>81.225959894138484</v>
+      </c>
+      <c r="F49" s="21">
+        <f t="shared" si="5"/>
+        <v>318.7740401058615</v>
+      </c>
+      <c r="G49" s="21">
+        <f t="shared" si="4"/>
+        <v>25763.8252757232</v>
+      </c>
+      <c r="H49" s="21">
+        <f t="shared" si="2"/>
+        <v>14236.1747242768</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A50" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B50" s="23">
+        <f t="shared" si="3"/>
+        <v>49</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E50" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F50" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G50" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H50" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D50" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="1"/>
+        <v>80.233239533586939</v>
+      </c>
+      <c r="F50" s="4">
+        <f t="shared" si="5"/>
+        <v>319.76676046641307</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="4"/>
+        <v>25444.058515256787</v>
+      </c>
+      <c r="H50" s="4">
+        <f t="shared" si="2"/>
+        <v>14555.941484743213</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A51" s="19">
+        <v>46240</v>
+      </c>
+      <c r="B51" s="24">
+        <f t="shared" si="3"/>
+        <v>50</v>
       </c>
       <c r="C51" s="20"/>
-      <c r="D51" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E51" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F51" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G51" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H51" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D51" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E51" s="21">
+        <f t="shared" si="1"/>
+        <v>79.237427661211143</v>
+      </c>
+      <c r="F51" s="21">
+        <f t="shared" si="5"/>
+        <v>320.76257233878886</v>
+      </c>
+      <c r="G51" s="21">
+        <f t="shared" si="4"/>
+        <v>25123.295942917997</v>
+      </c>
+      <c r="H51" s="21">
+        <f t="shared" si="2"/>
+        <v>14876.704057082003</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A52" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B52" s="23">
+        <f t="shared" si="3"/>
+        <v>51</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E52" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F52" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G52" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H52" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D52" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="1"/>
+        <v>78.238514649480777</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="5"/>
+        <v>321.76148535051925</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="4"/>
+        <v>24801.534457567479</v>
+      </c>
+      <c r="H52" s="4">
+        <f t="shared" si="2"/>
+        <v>15198.465542432521</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
-      <c r="B53" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A53" s="19">
+        <v>46240</v>
+      </c>
+      <c r="B53" s="24">
+        <f t="shared" si="3"/>
+        <v>52</v>
       </c>
       <c r="C53" s="20"/>
-      <c r="D53" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E53" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F53" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G53" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H53" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D53" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E53" s="21">
+        <f t="shared" si="1"/>
+        <v>77.236490840883661</v>
+      </c>
+      <c r="F53" s="21">
+        <f t="shared" si="5"/>
+        <v>322.76350915911632</v>
+      </c>
+      <c r="G53" s="21">
+        <f t="shared" si="4"/>
+        <v>24478.770948408364</v>
+      </c>
+      <c r="H53" s="21">
+        <f t="shared" si="2"/>
+        <v>15521.229051591636</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A54" s="2">
+        <v>46240</v>
+      </c>
+      <c r="B54" s="23">
+        <f t="shared" si="3"/>
+        <v>53</v>
       </c>
       <c r="C54" s="3"/>
-      <c r="D54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E54" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F54" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G54" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H54" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D54" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="1"/>
+        <v>76.231346547832345</v>
+      </c>
+      <c r="F54" s="4">
+        <f t="shared" si="5"/>
+        <v>323.76865345216765</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="4"/>
+        <v>24155.002294956197</v>
+      </c>
+      <c r="H54" s="4">
+        <f t="shared" si="2"/>
+        <v>15844.997705043803</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
@@ -8044,4 +8096,633 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46241</v>
+      </c>
+      <c r="B2" s="23">
+        <f>IF(A2&lt;&gt;"",1,"")</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:D18" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
+        <v>1400</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
+        <v>401.03124158893064</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
+        <v>998.9687584110693</v>
+      </c>
+      <c r="G2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
+        <v>19001.031241588931</v>
+      </c>
+      <c r="H2" s="4">
+        <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
+        <v>998.96875841106885</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="26" t="str">
+        <f ca="1">IF(K3&lt;&gt;"",
+   "L" &amp; TEXT(K7,"0") &amp;
+   IF(J10="Weeks","W","D") &amp; K10 &amp;
+   "-" &amp; K3 &amp;
+   "-N" &amp; RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1))),
+   "")</f>
+        <v>L20000W17-kamala-N204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="19"/>
+      <c r="B3" s="24" t="str">
+        <f>IF(A3&lt;&gt;"",B2+1,"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E3" s="21" t="str">
+        <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="21" t="str">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="21" t="str">
+        <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21" t="str">
+        <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="23" t="str">
+        <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F4" s="4" t="str">
+        <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="4" t="str">
+        <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="27"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E5" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F5" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G5" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H5" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="27"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G6" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="27"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E7" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F7" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G7" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="28">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H8" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="29">
+        <f>RATE(K10,-K9,K7)</f>
+        <v>2.0051562079446531E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E9" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G9" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="30">
+        <v>1400</v>
+      </c>
+      <c r="L9" s="22"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E10" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G10" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E11" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F11" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G11" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G12" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="10">
+        <f>IFERROR(MAX($B:$B),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E13" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F13" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G13" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="12">
+        <f>(K10*K9)-K9*K12</f>
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G14" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="12">
+        <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
+        <v>19001.031241588931</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19"/>
+      <c r="B15" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E15" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F15" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G15" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K15" s="14">
+        <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
+        <v>998.96875841106885</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="16">
+        <f>IF(A2,A2, "")</f>
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F17" s="21" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G17" s="21" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="18">
+        <f xml:space="preserve"> IF(A2,(K16 + (17*7)),"")</f>
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4917,7 +4917,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>26800</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>24155.002294956197</v>
+        <v>20526.305336742687</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>15844.997705043803</v>
+        <v>19473.694663257313</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -6218,311 +6218,333 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
-      <c r="B55" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A55" s="19">
+        <v>46245</v>
+      </c>
+      <c r="B55" s="24">
+        <f t="shared" si="3"/>
+        <v>54</v>
       </c>
       <c r="C55" s="20"/>
-      <c r="D55" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E55" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F55" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G55" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H55" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D55" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E55" s="21">
+        <f t="shared" si="1"/>
+        <v>75.223072052570487</v>
+      </c>
+      <c r="F55" s="21">
+        <f t="shared" si="5"/>
+        <v>324.7769279474295</v>
+      </c>
+      <c r="G55" s="21">
+        <f t="shared" si="4"/>
+        <v>23830.225367008767</v>
+      </c>
+      <c r="H55" s="21">
+        <f t="shared" si="2"/>
+        <v>16169.774632991233</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A56" s="2">
+        <v>46245</v>
+      </c>
+      <c r="B56" s="23">
+        <f t="shared" si="3"/>
+        <v>55</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E56" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F56" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G56" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H56" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D56" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E56" s="4">
+        <f t="shared" si="1"/>
+        <v>74.211657607078862</v>
+      </c>
+      <c r="F56" s="4">
+        <f t="shared" si="5"/>
+        <v>325.78834239292115</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="4"/>
+        <v>23504.437024615847</v>
+      </c>
+      <c r="H56" s="4">
+        <f t="shared" si="2"/>
+        <v>16495.562975384153</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
-      <c r="B57" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A57" s="19">
+        <v>46245</v>
+      </c>
+      <c r="B57" s="24">
+        <f t="shared" si="3"/>
+        <v>56</v>
       </c>
       <c r="C57" s="20"/>
-      <c r="D57" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E57" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F57" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G57" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H57" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D57" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E57" s="21">
+        <f t="shared" si="1"/>
+        <v>73.197093432981163</v>
+      </c>
+      <c r="F57" s="21">
+        <f t="shared" si="5"/>
+        <v>326.80290656701885</v>
+      </c>
+      <c r="G57" s="21">
+        <f t="shared" si="4"/>
+        <v>23177.634118048827</v>
+      </c>
+      <c r="H57" s="21">
+        <f t="shared" si="2"/>
+        <v>16822.365881951173</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A58" s="2">
+        <v>46245</v>
+      </c>
+      <c r="B58" s="23">
+        <f t="shared" si="3"/>
+        <v>57</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E58" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F58" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G58" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H58" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D58" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E58" s="4">
+        <f t="shared" si="1"/>
+        <v>72.179369721449433</v>
+      </c>
+      <c r="F58" s="4">
+        <f t="shared" si="5"/>
+        <v>327.82063027855054</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="4"/>
+        <v>22849.813487770276</v>
+      </c>
+      <c r="H58" s="4">
+        <f t="shared" si="2"/>
+        <v>17150.186512229724</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="19"/>
-      <c r="B59" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A59" s="19">
+        <v>46245</v>
+      </c>
+      <c r="B59" s="24">
+        <f t="shared" si="3"/>
+        <v>58</v>
       </c>
       <c r="C59" s="20"/>
-      <c r="D59" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E59" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F59" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G59" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H59" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D59" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E59" s="21">
+        <f t="shared" si="1"/>
+        <v>71.158476633109231</v>
+      </c>
+      <c r="F59" s="21">
+        <f t="shared" si="5"/>
+        <v>328.84152336689078</v>
+      </c>
+      <c r="G59" s="21">
+        <f t="shared" si="4"/>
+        <v>22520.971964403387</v>
+      </c>
+      <c r="H59" s="21">
+        <f t="shared" si="2"/>
+        <v>17479.028035596613</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A60" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B60" s="23">
+        <f t="shared" si="3"/>
+        <v>59</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E60" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F60" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G60" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H60" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D60" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E60" s="4">
+        <f t="shared" si="1"/>
+        <v>70.134404297944528</v>
+      </c>
+      <c r="F60" s="4">
+        <f t="shared" si="5"/>
+        <v>329.86559570205549</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="4"/>
+        <v>22191.10636870133</v>
+      </c>
+      <c r="H60" s="4">
+        <f t="shared" si="2"/>
+        <v>17808.89363129867</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="19"/>
-      <c r="B61" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A61" s="19">
+        <v>46251</v>
+      </c>
+      <c r="B61" s="24">
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="C61" s="20"/>
-      <c r="D61" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E61" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F61" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G61" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H61" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D61" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E61" s="21">
+        <f t="shared" si="1"/>
+        <v>69.107142815202252</v>
+      </c>
+      <c r="F61" s="21">
+        <f t="shared" si="5"/>
+        <v>330.89285718479778</v>
+      </c>
+      <c r="G61" s="21">
+        <f t="shared" si="4"/>
+        <v>21860.213511516533</v>
+      </c>
+      <c r="H61" s="21">
+        <f t="shared" si="2"/>
+        <v>18139.786488483467</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="2"/>
-      <c r="B62" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A62" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B62" s="23">
+        <f t="shared" si="3"/>
+        <v>61</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E62" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F62" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G62" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H62" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D62" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E62" s="4">
+        <f t="shared" si="1"/>
+        <v>68.076682253296596</v>
+      </c>
+      <c r="F62" s="4">
+        <f t="shared" si="5"/>
+        <v>331.92331774670339</v>
+      </c>
+      <c r="G62" s="4">
+        <f t="shared" si="4"/>
+        <v>21528.29019376983</v>
+      </c>
+      <c r="H62" s="4">
+        <f t="shared" si="2"/>
+        <v>18471.70980623017</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
-      <c r="B63" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A63" s="19">
+        <v>46251</v>
+      </c>
+      <c r="B63" s="24">
+        <f t="shared" si="3"/>
+        <v>62</v>
       </c>
       <c r="C63" s="20"/>
-      <c r="D63" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E63" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F63" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G63" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H63" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D63" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E63" s="21">
+        <f t="shared" si="1"/>
+        <v>67.043012649712978</v>
+      </c>
+      <c r="F63" s="21">
+        <f t="shared" si="5"/>
+        <v>332.95698735028702</v>
+      </c>
+      <c r="G63" s="21">
+        <f t="shared" si="4"/>
+        <v>21195.333206419542</v>
+      </c>
+      <c r="H63" s="21">
+        <f t="shared" si="2"/>
+        <v>18804.666793580458</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A64" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B64" s="23">
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="C64" s="3"/>
-      <c r="D64" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E64" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F64" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G64" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H64" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D64" s="4">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E64" s="4">
+        <f t="shared" si="1"/>
+        <v>66.006124010911762</v>
+      </c>
+      <c r="F64" s="4">
+        <f t="shared" si="5"/>
+        <v>333.99387598908822</v>
+      </c>
+      <c r="G64" s="4">
+        <f t="shared" si="4"/>
+        <v>20861.339330430455</v>
+      </c>
+      <c r="H64" s="4">
+        <f t="shared" si="2"/>
+        <v>19138.660669569545</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="19"/>
-      <c r="B65" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A65" s="19">
+        <v>46251</v>
+      </c>
+      <c r="B65" s="24">
+        <f t="shared" si="3"/>
+        <v>64</v>
       </c>
       <c r="C65" s="20"/>
-      <c r="D65" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E65" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F65" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G65" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H65" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D65" s="21">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E65" s="21">
+        <f t="shared" si="1"/>
+        <v>64.966006312231585</v>
+      </c>
+      <c r="F65" s="21">
+        <f t="shared" si="5"/>
+        <v>335.03399368776843</v>
+      </c>
+      <c r="G65" s="21">
+        <f t="shared" si="4"/>
+        <v>20526.305336742687</v>
+      </c>
+      <c r="H65" s="21">
+        <f t="shared" si="2"/>
+        <v>19473.694663257313</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -8188,31 +8210,33 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="24" t="str">
+      <c r="A3" s="19">
+        <v>46248</v>
+      </c>
+      <c r="B3" s="24">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>381.00035751422342</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>1018.9996424857766</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>17982.031599103153</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>2017.968400896847</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>10</v>
@@ -8222,31 +8246,33 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="23" t="str">
+      <c r="A4" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B4" s="23">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="4" t="str">
+      <c r="D4" s="4">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="1"/>
+        <v>360.56782292398606</v>
+      </c>
+      <c r="F4" s="4">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="4" t="str">
+        <v>1039.4321770760139</v>
+      </c>
+      <c r="G4" s="4">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>16942.599422027139</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="2"/>
+        <v>3057.4005779728614</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>11</v>
@@ -8516,7 +8542,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8551,7 +8577,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>22400</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8586,7 +8612,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>19001.031241588931</v>
+        <v>16942.599422027139</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8621,7 +8647,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>998.96875841106885</v>
+        <v>3057.4005779728614</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Kamala_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Kamala_Daily.xlsx
@@ -4917,7 +4917,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>22400</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>20526.305336742687</v>
+        <v>13244.497417797626</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>19473.694663257313</v>
+        <v>26755.502582202374</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -6369,7 +6369,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B60" s="23">
         <f t="shared" si="3"/>
@@ -6399,7 +6399,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="19">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B61" s="24">
         <f t="shared" si="3"/>
@@ -6429,7 +6429,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B62" s="23">
         <f t="shared" si="3"/>
@@ -6459,7 +6459,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="19">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B63" s="24">
         <f t="shared" si="3"/>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B64" s="23">
         <f t="shared" si="3"/>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="19">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B65" s="24">
         <f t="shared" si="3"/>
@@ -6548,591 +6548,633 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A66" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B66" s="23">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="4" t="str">
+      <c r="D66" s="4">
         <f t="shared" ref="D66:D121" si="6">IF(AND($A66&lt;&gt;"",$B66&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E66" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F66" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G66" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H66" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>400</v>
+      </c>
+      <c r="E66" s="4">
+        <f t="shared" si="1"/>
+        <v>63.922649497792449</v>
+      </c>
+      <c r="F66" s="4">
+        <f t="shared" si="5"/>
+        <v>336.07735050220754</v>
+      </c>
+      <c r="G66" s="4">
+        <f t="shared" si="4"/>
+        <v>20190.227986240479</v>
+      </c>
+      <c r="H66" s="4">
+        <f t="shared" si="2"/>
+        <v>19809.772013759521</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="19"/>
-      <c r="B67" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A67" s="19">
+        <v>46257</v>
+      </c>
+      <c r="B67" s="24">
+        <f t="shared" si="3"/>
+        <v>66</v>
       </c>
       <c r="C67" s="20"/>
-      <c r="D67" s="21" t="str">
+      <c r="D67" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E67" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E67" s="21">
         <f t="shared" ref="E67:E121" si="7">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),G66*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G67" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H67" s="21" t="str">
+        <v>62.87604348039855</v>
+      </c>
+      <c r="F67" s="21">
+        <f t="shared" si="5"/>
+        <v>337.12395651960145</v>
+      </c>
+      <c r="G67" s="21">
+        <f t="shared" si="4"/>
+        <v>19853.104029720878</v>
+      </c>
+      <c r="H67" s="21">
         <f t="shared" ref="H67:H121" si="8">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),$K$7-G67,"")</f>
-        <v/>
+        <v>20146.895970279122</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
-      <c r="B68" s="23" t="str">
+      <c r="A68" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B68" s="23">
         <f t="shared" ref="B68:B121" si="9">IF(A68&lt;&gt;"",B67+1,"")</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="4" t="str">
+      <c r="D68" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E68" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E68" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F68" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G68" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H68" s="4" t="str">
+        <v>61.826178141440714</v>
+      </c>
+      <c r="F68" s="4">
+        <f t="shared" si="5"/>
+        <v>338.17382185855928</v>
+      </c>
+      <c r="G68" s="4">
+        <f t="shared" si="4"/>
+        <v>19514.930207862319</v>
+      </c>
+      <c r="H68" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20485.069792137681</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="19"/>
-      <c r="B69" s="24" t="str">
+      <c r="A69" s="19">
+        <v>46257</v>
+      </c>
+      <c r="B69" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>68</v>
       </c>
       <c r="C69" s="20"/>
-      <c r="D69" s="21" t="str">
+      <c r="D69" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E69" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E69" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F69" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G69" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H69" s="21" t="str">
+        <v>60.773043330798551</v>
+      </c>
+      <c r="F69" s="21">
+        <f t="shared" si="5"/>
+        <v>339.22695666920146</v>
+      </c>
+      <c r="G69" s="21">
+        <f t="shared" si="4"/>
+        <v>19175.703251193117</v>
+      </c>
+      <c r="H69" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20824.296748806883</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
-      <c r="B70" s="23" t="str">
+      <c r="A70" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B70" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>69</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="4" t="str">
+      <c r="D70" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E70" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E70" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F70" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G70" s="4" t="str">
+        <v>59.71662886674239</v>
+      </c>
+      <c r="F70" s="4">
+        <f t="shared" si="5"/>
+        <v>340.28337113325762</v>
+      </c>
+      <c r="G70" s="4">
         <f t="shared" ref="G70:G121" si="10">IF(AND($A70&lt;&gt;"",$B70&lt;&gt;""),G69-F70,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="4" t="str">
+        <v>18835.419880059861</v>
+      </c>
+      <c r="H70" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21164.580119940139</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="19"/>
-      <c r="B71" s="24" t="str">
+      <c r="A71" s="19">
+        <v>46262</v>
+      </c>
+      <c r="B71" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>70</v>
       </c>
       <c r="C71" s="20"/>
-      <c r="D71" s="21" t="str">
+      <c r="D71" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E71" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E71" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F71" s="21" t="str">
+        <v>58.656924535834776</v>
+      </c>
+      <c r="F71" s="21">
         <f t="shared" ref="F71:F121" si="11">IF(AND($A71&lt;&gt;"",$B71&lt;&gt;""),D71-E71,"")</f>
-        <v/>
-      </c>
-      <c r="G71" s="21" t="str">
+        <v>341.34307546416522</v>
+      </c>
+      <c r="G71" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H71" s="21" t="str">
+        <v>18494.076804595694</v>
+      </c>
+      <c r="H71" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21505.923195404306</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
-      <c r="B72" s="23" t="str">
+      <c r="A72" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B72" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>71</v>
       </c>
       <c r="C72" s="3"/>
-      <c r="D72" s="4" t="str">
+      <c r="D72" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E72" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E72" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F72" s="4" t="str">
+        <v>57.593920092831738</v>
+      </c>
+      <c r="F72" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G72" s="4" t="str">
+        <v>342.40607990716825</v>
+      </c>
+      <c r="G72" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H72" s="4" t="str">
+        <v>18151.670724688527</v>
+      </c>
+      <c r="H72" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21848.329275311473</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="19"/>
-      <c r="B73" s="24" t="str">
+      <c r="A73" s="19">
+        <v>46262</v>
+      </c>
+      <c r="B73" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>72</v>
       </c>
       <c r="C73" s="20"/>
-      <c r="D73" s="21" t="str">
+      <c r="D73" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E73" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E73" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F73" s="21" t="str">
+        <v>56.527605260583783</v>
+      </c>
+      <c r="F73" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G73" s="21" t="str">
+        <v>343.47239473941625</v>
+      </c>
+      <c r="G73" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H73" s="21" t="str">
+        <v>17808.198329949111</v>
+      </c>
+      <c r="H73" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22191.801670050889</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2"/>
-      <c r="B74" s="23" t="str">
+      <c r="A74" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B74" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>73</v>
       </c>
       <c r="C74" s="3"/>
-      <c r="D74" s="4" t="str">
+      <c r="D74" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E74" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E74" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F74" s="4" t="str">
+        <v>55.457969729936494</v>
+      </c>
+      <c r="F74" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G74" s="4" t="str">
+        <v>344.54203027006349</v>
+      </c>
+      <c r="G74" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H74" s="4" t="str">
+        <v>17463.656299679049</v>
+      </c>
+      <c r="H74" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22536.343700320951</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="19"/>
-      <c r="B75" s="24" t="str">
+      <c r="A75" s="19">
+        <v>46262</v>
+      </c>
+      <c r="B75" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>74</v>
       </c>
       <c r="C75" s="20"/>
-      <c r="D75" s="21" t="str">
+      <c r="D75" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E75" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E75" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F75" s="21" t="str">
+        <v>54.385003159630863</v>
+      </c>
+      <c r="F75" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G75" s="21" t="str">
+        <v>345.61499684036914</v>
+      </c>
+      <c r="G75" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H75" s="21" t="str">
+        <v>17118.041302838679</v>
+      </c>
+      <c r="H75" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22881.958697161321</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2"/>
-      <c r="B76" s="23" t="str">
+      <c r="A76" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B76" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>75</v>
       </c>
       <c r="C76" s="3"/>
-      <c r="D76" s="4" t="str">
+      <c r="D76" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E76" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E76" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F76" s="4" t="str">
+        <v>53.308695176203315</v>
+      </c>
+      <c r="F76" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G76" s="4" t="str">
+        <v>346.69130482379671</v>
+      </c>
+      <c r="G76" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H76" s="4" t="str">
+        <v>16771.349998014881</v>
+      </c>
+      <c r="H76" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23228.650001985119</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="19"/>
-      <c r="B77" s="24" t="str">
+      <c r="A77" s="19">
+        <v>46269</v>
+      </c>
+      <c r="B77" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>76</v>
       </c>
       <c r="C77" s="20"/>
-      <c r="D77" s="21" t="str">
+      <c r="D77" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E77" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E77" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F77" s="21" t="str">
+        <v>52.229035373885438</v>
+      </c>
+      <c r="F77" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G77" s="21" t="str">
+        <v>347.77096462611456</v>
+      </c>
+      <c r="G77" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H77" s="21" t="str">
+        <v>16423.579033388767</v>
+      </c>
+      <c r="H77" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23576.420966611233</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
-      <c r="B78" s="23" t="str">
+      <c r="A78" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B78" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>77</v>
       </c>
       <c r="C78" s="3"/>
-      <c r="D78" s="4" t="str">
+      <c r="D78" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E78" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E78" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F78" s="4" t="str">
+        <v>51.146013314503371</v>
+      </c>
+      <c r="F78" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G78" s="4" t="str">
+        <v>348.85398668549664</v>
+      </c>
+      <c r="G78" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H78" s="4" t="str">
+        <v>16074.72504670327</v>
+      </c>
+      <c r="H78" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23925.274953296728</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="19"/>
-      <c r="B79" s="24" t="str">
+      <c r="A79" s="19">
+        <v>46269</v>
+      </c>
+      <c r="B79" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>78</v>
       </c>
       <c r="C79" s="20"/>
-      <c r="D79" s="21" t="str">
+      <c r="D79" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E79" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E79" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F79" s="21" t="str">
+        <v>50.059618527376848</v>
+      </c>
+      <c r="F79" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G79" s="21" t="str">
+        <v>349.94038147262313</v>
+      </c>
+      <c r="G79" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H79" s="21" t="str">
+        <v>15724.784665230647</v>
+      </c>
+      <c r="H79" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>24275.215334769353</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="2"/>
-      <c r="B80" s="23" t="str">
+      <c r="A80" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B80" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>79</v>
       </c>
       <c r="C80" s="3"/>
-      <c r="D80" s="4" t="str">
+      <c r="D80" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E80" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E80" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F80" s="4" t="str">
+        <v>48.969840509218024</v>
+      </c>
+      <c r="F80" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G80" s="4" t="str">
+        <v>351.03015949078195</v>
+      </c>
+      <c r="G80" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H80" s="4" t="str">
+        <v>15373.754505739866</v>
+      </c>
+      <c r="H80" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>24626.245494260133</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="19"/>
-      <c r="B81" s="24" t="str">
+      <c r="A81" s="19">
+        <v>46269</v>
+      </c>
+      <c r="B81" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>80</v>
       </c>
       <c r="C81" s="20"/>
-      <c r="D81" s="21" t="str">
+      <c r="D81" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E81" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E81" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F81" s="21" t="str">
+        <v>47.876668724029912</v>
+      </c>
+      <c r="F81" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G81" s="21" t="str">
+        <v>352.12333127597009</v>
+      </c>
+      <c r="G81" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H81" s="21" t="str">
+        <v>15021.631174463895</v>
+      </c>
+      <c r="H81" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>24978.368825536105</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="2"/>
-      <c r="B82" s="23" t="str">
+      <c r="A82" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B82" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>81</v>
       </c>
       <c r="C82" s="3"/>
-      <c r="D82" s="4" t="str">
+      <c r="D82" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E82" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E82" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F82" s="4" t="str">
+        <v>46.780092603004476</v>
+      </c>
+      <c r="F82" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G82" s="4" t="str">
+        <v>353.2199073969955</v>
+      </c>
+      <c r="G82" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H82" s="4" t="str">
+        <v>14668.4112670669</v>
+      </c>
+      <c r="H82" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>25331.588732933102</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="19"/>
-      <c r="B83" s="24" t="str">
+      <c r="A83" s="19">
+        <v>46274</v>
+      </c>
+      <c r="B83" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>82</v>
       </c>
       <c r="C83" s="20"/>
-      <c r="D83" s="21" t="str">
+      <c r="D83" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E83" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E83" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F83" s="21" t="str">
+        <v>45.680101544420538</v>
+      </c>
+      <c r="F83" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G83" s="21" t="str">
+        <v>354.31989845557945</v>
+      </c>
+      <c r="G83" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H83" s="21" t="str">
+        <v>14314.09136861132</v>
+      </c>
+      <c r="H83" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>25685.90863138868</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="2"/>
-      <c r="B84" s="23" t="str">
+      <c r="A84" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B84" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>83</v>
       </c>
       <c r="C84" s="3"/>
-      <c r="D84" s="4" t="str">
+      <c r="D84" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E84" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E84" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F84" s="4" t="str">
+        <v>44.576684913541186</v>
+      </c>
+      <c r="F84" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G84" s="4" t="str">
+        <v>355.42331508645884</v>
+      </c>
+      <c r="G84" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H84" s="4" t="str">
+        <v>13958.668053524862</v>
+      </c>
+      <c r="H84" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>26041.33194647514</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="19"/>
-      <c r="B85" s="24" t="str">
+      <c r="A85" s="19">
+        <v>46274</v>
+      </c>
+      <c r="B85" s="24">
         <f t="shared" si="9"/>
-        <v/>
+        <v>84</v>
       </c>
       <c r="C85" s="20"/>
-      <c r="D85" s="21" t="str">
+      <c r="D85" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E85" s="21" t="str">
+        <v>400</v>
+      </c>
+      <c r="E85" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F85" s="21" t="str">
+        <v>43.469832042511037</v>
+      </c>
+      <c r="F85" s="21">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G85" s="21" t="str">
+        <v>356.53016795748897</v>
+      </c>
+      <c r="G85" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H85" s="21" t="str">
+        <v>13602.137885567372</v>
+      </c>
+      <c r="H85" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>26397.862114432628</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="2"/>
-      <c r="B86" s="23" t="str">
+      <c r="A86" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B86" s="23">
         <f t="shared" si="9"/>
-        <v/>
+        <v>85</v>
       </c>
       <c r="C86" s="3"/>
-      <c r="D86" s="4" t="str">
+      <c r="D86" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E86" s="4" t="str">
+        <v>400</v>
+      </c>
+      <c r="E86" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F86" s="4" t="str">
+        <v>42.359532230253038</v>
+      </c>
+      <c r="F86" s="4">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="G86" s="4" t="str">
+        <v>357.64046776974698</v>
+      </c>
+      <c r="G86" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H86" s="4" t="str">
+        <v>13244.497417797626</v>
+      </c>
+      <c r="H86" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>26755.502582202374</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
@@ -8280,31 +8322,33 @@
       <c r="K4" s="27"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46262</v>
+      </c>
+      <c r="B5" s="24">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>339.7255840979721</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="4"/>
+        <v>1060.2744159020278</v>
+      </c>
+      <c r="G5" s="21">
+        <f t="shared" si="5"/>
+        <v>15882.325006125111</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>4117.674993874889</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>12</v>
@@ -8312,31 +8356,33 @@
       <c r="K5" s="27"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="1"/>
+        <v>318.4654258262637</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="4"/>
+        <v>1081.5345741737362</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="5"/>
+        <v>14800.790431951375</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="2"/>
+        <v>5199.2095680486254</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>13</v>
@@ -8344,31 +8390,33 @@
       <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46276</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>296.77896817115123</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="4"/>
+        <v>1103.2210318288487</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="5"/>
+        <v>13697.569400122526</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>6302.4305998774744</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>7</v>
@@ -8542,7 +8590,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8577,7 +8625,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>19600</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8612,7 +8660,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>16942.599422027139</v>
+        <v>13697.569400122526</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8647,7 +8695,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3057.4005779728614</v>
+        <v>6302.4305998774744</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
